--- a/docs/data/jp/xlsx/6798.xlsx
+++ b/docs/data/jp/xlsx/6798.xlsx
@@ -13431,7 +13431,7 @@
     <row r="192">
       <c r="A192" s="18" t="inlineStr">
         <is>
-          <t>CSReportableSegmentsMember · Operating Income</t>
+          <t>CSReportableSegmentsMember · 부문 이익 또는 손실(△)(영업손실)</t>
         </is>
       </c>
       <c r="C192" s="20" t="n">
@@ -13611,7 +13611,7 @@
     <row r="195">
       <c r="A195" s="18" t="inlineStr">
         <is>
-          <t>SCIReportableSegmentMember · Operating Income</t>
+          <t>SCIReportableSegmentMember · 부문 이익 또는 손실(△)(영업손실)</t>
         </is>
       </c>
       <c r="C195" s="20" t="n">
@@ -13791,7 +13791,7 @@
     <row r="198">
       <c r="A198" s="18" t="inlineStr">
         <is>
-          <t>RandDCenterReportableSegmentsMember · Operating Income</t>
+          <t>RandDCenterReportableSegmentsMember · 부문 이익 또는 손실(△)(영업손실)</t>
         </is>
       </c>
       <c r="E198" s="20" t="n">
@@ -13880,7 +13880,7 @@
     <row r="201">
       <c r="A201" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · Operating Income</t>
+          <t>보고부문 합계 · 부문 이익 또는 손실(△)(영업손실)</t>
         </is>
       </c>
       <c r="C201" s="20" t="n">
@@ -14060,7 +14060,7 @@
     <row r="204">
       <c r="A204" s="18" t="inlineStr">
         <is>
-          <t>EntityTotalMember · Operating Income</t>
+          <t>EntityTotalMember · 부문 이익 또는 손실(△)(영업손실)</t>
         </is>
       </c>
       <c r="E204" s="20" t="n">
@@ -14076,7 +14076,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>Operating Income</t>
+          <t>부문 이익 또는 손실(△)(영업손실)</t>
         </is>
       </c>
       <c r="C205" s="12" t="n">
@@ -14623,7 +14623,7 @@
     <row r="217">
       <c r="A217" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Valuation Reserve For Inventory Purchase Commitments Ope CF</t>
+          <t>매입계약 평가충당금 증감(△는 감소)</t>
         </is>
       </c>
       <c r="D217" s="20" t="n">
@@ -21472,7 +21472,7 @@
     <row r="122">
       <c r="A122" s="18" t="inlineStr">
         <is>
-          <t>Valuation Reserve For Inventory Purchase Commitments CL</t>
+          <t>매입계약 평가충당금</t>
         </is>
       </c>
       <c r="C122" s="20" t="n">
